--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1569,6 +1569,228 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120286994</v>
+      </c>
+      <c r="B10" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sarvisvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>789563</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7421480</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120286985</v>
+      </c>
+      <c r="B11" t="n">
+        <v>97907</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sarvisvaara, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>789361</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7421760</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>120286994</v>
       </c>
       <c r="B10" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1685,7 +1685,7 @@
         <v>120286985</v>
       </c>
       <c r="B11" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286994</v>
+        <v>120286985</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789563</v>
+        <v>789361</v>
       </c>
       <c r="R10" t="n">
-        <v>7421480</v>
+        <v>7421760</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286985</v>
+        <v>120286994</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789361</v>
+        <v>789563</v>
       </c>
       <c r="R11" t="n">
-        <v>7421760</v>
+        <v>7421480</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1571,7 +1571,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286985</v>
+        <v>120286994</v>
       </c>
       <c r="B10" t="n">
         <v>97930</v>
@@ -1606,7 +1606,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1615,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789361</v>
+        <v>789563</v>
       </c>
       <c r="R10" t="n">
-        <v>7421760</v>
+        <v>7421480</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1682,7 +1682,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286994</v>
+        <v>120286985</v>
       </c>
       <c r="B11" t="n">
         <v>97930</v>
@@ -1717,7 +1717,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789563</v>
+        <v>789361</v>
       </c>
       <c r="R11" t="n">
-        <v>7421480</v>
+        <v>7421760</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152571</v>
+        <v>121152570</v>
       </c>
       <c r="B12" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789307</v>
+        <v>789274</v>
       </c>
       <c r="R12" t="n">
-        <v>7421740</v>
+        <v>7421710</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152570</v>
+        <v>121152571</v>
       </c>
       <c r="B13" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789274</v>
+        <v>789307</v>
       </c>
       <c r="R13" t="n">
-        <v>7421710</v>
+        <v>7421740</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2018,7 +2018,7 @@
         <v>121152569</v>
       </c>
       <c r="B14" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152574</v>
+        <v>121152573</v>
       </c>
       <c r="B15" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789269</v>
+        <v>789325</v>
       </c>
       <c r="R15" t="n">
-        <v>7421730</v>
+        <v>7421750</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152573</v>
+        <v>121152574</v>
       </c>
       <c r="B16" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789325</v>
+        <v>789269</v>
       </c>
       <c r="R16" t="n">
-        <v>7421750</v>
+        <v>7421730</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152570</v>
+        <v>121152573</v>
       </c>
       <c r="B12" t="n">
         <v>98081</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789274</v>
+        <v>789325</v>
       </c>
       <c r="R12" t="n">
-        <v>7421710</v>
+        <v>7421750</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152573</v>
+        <v>121152574</v>
       </c>
       <c r="B15" t="n">
         <v>98081</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789325</v>
+        <v>789269</v>
       </c>
       <c r="R15" t="n">
-        <v>7421750</v>
+        <v>7421730</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152574</v>
+        <v>121152570</v>
       </c>
       <c r="B16" t="n">
         <v>98081</v>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789269</v>
+        <v>789274</v>
       </c>
       <c r="R16" t="n">
-        <v>7421730</v>
+        <v>7421710</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152573</v>
+        <v>121152570</v>
       </c>
       <c r="B12" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789325</v>
+        <v>789274</v>
       </c>
       <c r="R12" t="n">
-        <v>7421750</v>
+        <v>7421710</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152571</v>
+        <v>121152573</v>
       </c>
       <c r="B13" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789307</v>
+        <v>789325</v>
       </c>
       <c r="R13" t="n">
-        <v>7421740</v>
+        <v>7421750</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2018,7 +2018,7 @@
         <v>121152569</v>
       </c>
       <c r="B14" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152574</v>
+        <v>121152571</v>
       </c>
       <c r="B15" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789269</v>
+        <v>789307</v>
       </c>
       <c r="R15" t="n">
-        <v>7421730</v>
+        <v>7421740</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152570</v>
+        <v>121152574</v>
       </c>
       <c r="B16" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789274</v>
+        <v>789269</v>
       </c>
       <c r="R16" t="n">
-        <v>7421710</v>
+        <v>7421730</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152570</v>
+        <v>121152571</v>
       </c>
       <c r="B12" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789274</v>
+        <v>789307</v>
       </c>
       <c r="R12" t="n">
-        <v>7421710</v>
+        <v>7421740</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152573</v>
+        <v>121152569</v>
       </c>
       <c r="B13" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789325</v>
+        <v>789279</v>
       </c>
       <c r="R13" t="n">
-        <v>7421750</v>
+        <v>7421700</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152569</v>
+        <v>121152570</v>
       </c>
       <c r="B14" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789279</v>
+        <v>789274</v>
       </c>
       <c r="R14" t="n">
-        <v>7421700</v>
+        <v>7421710</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,10 +2126,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152571</v>
+        <v>121152574</v>
       </c>
       <c r="B15" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2161,7 +2161,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789307</v>
+        <v>789269</v>
       </c>
       <c r="R15" t="n">
-        <v>7421740</v>
+        <v>7421730</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152574</v>
+        <v>121152573</v>
       </c>
       <c r="B16" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789269</v>
+        <v>789325</v>
       </c>
       <c r="R16" t="n">
-        <v>7421730</v>
+        <v>7421750</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,10 +1793,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152571</v>
+        <v>121152573</v>
       </c>
       <c r="B12" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789307</v>
+        <v>789325</v>
       </c>
       <c r="R12" t="n">
-        <v>7421740</v>
+        <v>7421750</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152569</v>
+        <v>121152570</v>
       </c>
       <c r="B13" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789279</v>
+        <v>789274</v>
       </c>
       <c r="R13" t="n">
-        <v>7421700</v>
+        <v>7421710</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2015,10 +2015,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152570</v>
+        <v>121152571</v>
       </c>
       <c r="B14" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789274</v>
+        <v>789307</v>
       </c>
       <c r="R14" t="n">
-        <v>7421710</v>
+        <v>7421740</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2129,7 +2129,7 @@
         <v>121152574</v>
       </c>
       <c r="B15" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2237,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152573</v>
+        <v>121152569</v>
       </c>
       <c r="B16" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789325</v>
+        <v>789279</v>
       </c>
       <c r="R16" t="n">
-        <v>7421750</v>
+        <v>7421700</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -1793,7 +1793,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152573</v>
+        <v>121152571</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789325</v>
+        <v>789307</v>
       </c>
       <c r="R12" t="n">
-        <v>7421750</v>
+        <v>7421740</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121152570</v>
+        <v>121152574</v>
       </c>
       <c r="B13" t="n">
         <v>98098</v>
@@ -1948,10 +1948,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>789274</v>
+        <v>789269</v>
       </c>
       <c r="R13" t="n">
-        <v>7421710</v>
+        <v>7421730</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2015,7 +2015,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121152571</v>
+        <v>121152570</v>
       </c>
       <c r="B14" t="n">
         <v>98098</v>
@@ -2050,7 +2050,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2059,10 +2059,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>789307</v>
+        <v>789274</v>
       </c>
       <c r="R14" t="n">
-        <v>7421740</v>
+        <v>7421710</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2126,7 +2126,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121152574</v>
+        <v>121152569</v>
       </c>
       <c r="B15" t="n">
         <v>98098</v>
@@ -2170,10 +2170,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>789269</v>
+        <v>789279</v>
       </c>
       <c r="R15" t="n">
-        <v>7421730</v>
+        <v>7421700</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2237,7 +2237,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121152569</v>
+        <v>121152573</v>
       </c>
       <c r="B16" t="n">
         <v>98098</v>
@@ -2281,10 +2281,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>789279</v>
+        <v>789325</v>
       </c>
       <c r="R16" t="n">
-        <v>7421700</v>
+        <v>7421750</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>

--- a/artfynd/A 34596-2024 artfynd.xlsx
+++ b/artfynd/A 34596-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1143,10 +1143,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112605802</v>
+        <v>120286985</v>
       </c>
       <c r="B6" t="n">
-        <v>89936</v>
+        <v>98001</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1155,41 +1155,45 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1588</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violmussling</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Trichaptum laricinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Ryvarden</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Sarvisvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>789355</v>
+        <v>789361</v>
       </c>
       <c r="R6" t="n">
-        <v>7421762</v>
+        <v>7421760</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1213,17 +1217,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1254,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>112605800</v>
+        <v>120286994</v>
       </c>
       <c r="B7" t="n">
-        <v>77608</v>
+        <v>98001</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1262,41 +1266,45 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sarvisvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>789267</v>
+        <v>789563</v>
       </c>
       <c r="R7" t="n">
-        <v>7421467</v>
+        <v>7421480</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1320,17 +1328,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1365,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112605784</v>
+        <v>121152571</v>
       </c>
       <c r="B8" t="n">
-        <v>91032</v>
+        <v>98098</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1369,41 +1377,45 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Sarvisvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>789440</v>
+        <v>789307</v>
       </c>
       <c r="R8" t="n">
-        <v>7421641</v>
+        <v>7421740</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1427,17 +1439,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1476,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112605801</v>
+        <v>121152574</v>
       </c>
       <c r="B9" t="n">
-        <v>95966</v>
+        <v>98098</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,41 +1488,45 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Sarvisvaara, Lu lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>789444</v>
+        <v>789269</v>
       </c>
       <c r="R9" t="n">
-        <v>7421550</v>
+        <v>7421730</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1534,17 +1550,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-10-20</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesbedömning</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1587,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120286985</v>
+        <v>121152570</v>
       </c>
       <c r="B10" t="n">
-        <v>98001</v>
+        <v>98098</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1615,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>789361</v>
+        <v>789274</v>
       </c>
       <c r="R10" t="n">
-        <v>7421760</v>
+        <v>7421710</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1645,17 +1661,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1682,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120286994</v>
+        <v>121152569</v>
       </c>
       <c r="B11" t="n">
-        <v>98001</v>
+        <v>98098</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1717,7 +1733,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1726,10 +1742,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>789563</v>
+        <v>789279</v>
       </c>
       <c r="R11" t="n">
-        <v>7421480</v>
+        <v>7421700</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1756,17 +1772,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-10-08</t>
+          <t>2024-10-07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering.</t>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1793,7 +1809,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121152571</v>
+        <v>121152573</v>
       </c>
       <c r="B12" t="n">
         <v>98098</v>
@@ -1828,7 +1844,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1837,10 +1853,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>789307</v>
+        <v>789325</v>
       </c>
       <c r="R12" t="n">
-        <v>7421740</v>
+        <v>7421750</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1901,450 +1917,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>121152574</v>
-      </c>
-      <c r="B13" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Sarvisvaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>789269</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7421730</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="n">
-        <v>121152570</v>
-      </c>
-      <c r="B14" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Sarvisvaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q14" t="n">
-        <v>789274</v>
-      </c>
-      <c r="R14" t="n">
-        <v>7421710</v>
-      </c>
-      <c r="S14" t="n">
-        <v>5</v>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT14" t="inlineStr"/>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>121152569</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Sarvisvaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>789279</v>
-      </c>
-      <c r="R15" t="n">
-        <v>7421700</v>
-      </c>
-      <c r="S15" t="n">
-        <v>5</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121152573</v>
-      </c>
-      <c r="B16" t="n">
-        <v>98098</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Sarvisvaara, Lu lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>789325</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7421750</v>
-      </c>
-      <c r="S16" t="n">
-        <v>5</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Norrbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Lule lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Gällivare</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-10-07</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Mimmi Persson</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
